--- a/Koszty/serwis_2026.xlsx
+++ b/Koszty/serwis_2026.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.gutowski\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6325AF-E0D7-4EBE-A640-011CDCAFEABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE26885-E109-4F8B-A9EF-3B8B08D32D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{829E7267-720C-45F6-988A-08D9E87A1D96}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{829E7267-720C-45F6-988A-08D9E87A1D96}"/>
   </bookViews>
   <sheets>
-    <sheet name="Arkusz4" sheetId="4" r:id="rId1"/>
+    <sheet name="2026" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Arkusz4!$B$3:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$3:$D$3</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="53">
   <si>
     <t>Tczew</t>
   </si>
@@ -207,7 +207,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,6 +237,22 @@
       <color theme="4"/>
       <name val="Czcionka tekstu podstawowego"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -323,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -355,13 +371,37 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -698,64 +738,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB6E47C7-5673-4B49-9C5E-F642709C392B}">
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:T67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="3"/>
     <col min="3" max="3" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3"/>
     <col min="7" max="7" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="4.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="3"/>
     <col min="11" max="11" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="4.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="3"/>
+    <col min="15" max="15" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="4.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="3"/>
+    <col min="19" max="19" width="22.7109375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="46.5" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:20" ht="46.5" customHeight="1">
+      <c r="A1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11" t="s">
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-    </row>
-    <row r="2" spans="1:12" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A2" s="13">
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+    </row>
+    <row r="2" spans="1:20" ht="46.5" customHeight="1" thickBot="1">
+      <c r="A2" s="20">
         <v>46023</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20">
         <v>46054</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="20">
         <v>46082</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-    </row>
-    <row r="3" spans="1:12" ht="30.75" thickBot="1">
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="20">
+        <v>46113</v>
+      </c>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="20">
+        <v>46143</v>
+      </c>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+    </row>
+    <row r="3" spans="1:20" ht="30.75" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>43</v>
       </c>
@@ -792,8 +864,32 @@
       <c r="L3" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -830,8 +926,32 @@
       <c r="L4" s="9">
         <v>380</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="6">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1101</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="9">
+        <v>380</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1101</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -868,8 +988,32 @@
       <c r="L5" s="9">
         <v>600</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="6">
+        <v>2</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1105</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="9">
+        <v>600</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>2</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1105</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -906,8 +1050,32 @@
       <c r="L6" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="6">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1106</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>3</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1106</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -944,8 +1112,32 @@
       <c r="L7" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7" s="6">
+        <v>4</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1108</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>4</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1108</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -961,13 +1153,13 @@
       <c r="E8" s="6">
         <v>5</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="15">
         <v>1109</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="17">
         <v>400</v>
       </c>
       <c r="I8" s="6">
@@ -982,8 +1174,32 @@
       <c r="L8" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8" s="6">
+        <v>5</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1109</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>5</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1109</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -1020,8 +1236,32 @@
       <c r="L9" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9" s="6">
+        <v>6</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1110</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>6</v>
+      </c>
+      <c r="R9" s="1">
+        <v>1110</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T9" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -1058,8 +1298,32 @@
       <c r="L10" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10" s="6">
+        <v>7</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1111</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>7</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1111</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -1096,8 +1360,32 @@
       <c r="L11" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11" s="6">
+        <v>8</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1112</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P11" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>8</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1112</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T11" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -1134,8 +1422,32 @@
       <c r="L12" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12" s="6">
+        <v>9</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1114</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>9</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1114</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -1172,8 +1484,32 @@
       <c r="L13" s="9">
         <v>380</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13" s="6">
+        <v>10</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1115</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="9">
+        <v>380</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>10</v>
+      </c>
+      <c r="R13" s="1">
+        <v>1115</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T13" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -1210,8 +1546,32 @@
       <c r="L14" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14" s="6">
+        <v>11</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1116</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>11</v>
+      </c>
+      <c r="R14" s="1">
+        <v>1116</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -1227,13 +1587,13 @@
       <c r="E15" s="6">
         <v>12</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="11">
         <v>1120</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="13">
         <v>380</v>
       </c>
       <c r="I15" s="6">
@@ -1248,8 +1608,32 @@
       <c r="L15" s="9">
         <v>380</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15" s="6">
+        <v>12</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1120</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P15" s="9">
+        <v>380</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>12</v>
+      </c>
+      <c r="R15" s="1">
+        <v>1120</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T15" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -1265,13 +1649,13 @@
       <c r="E16" s="6">
         <v>13</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="11">
         <v>1121</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="13">
         <v>380</v>
       </c>
       <c r="I16" s="6">
@@ -1286,8 +1670,32 @@
       <c r="L16" s="9">
         <v>380</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="6">
+        <v>13</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1121</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P16" s="9">
+        <v>380</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>13</v>
+      </c>
+      <c r="R16" s="1">
+        <v>1121</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T16" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -1324,8 +1732,32 @@
       <c r="L17" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="6">
+        <v>14</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1122</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>14</v>
+      </c>
+      <c r="R17" s="1">
+        <v>1122</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T17" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -1362,8 +1794,32 @@
       <c r="L18" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18" s="6">
+        <v>15</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1123</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>15</v>
+      </c>
+      <c r="R18" s="1">
+        <v>1123</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="T18" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -1400,8 +1856,32 @@
       <c r="L19" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19" s="6">
+        <v>16</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1135</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>16</v>
+      </c>
+      <c r="R19" s="1">
+        <v>1135</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T19" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20" s="6">
         <v>17</v>
       </c>
@@ -1417,13 +1897,13 @@
       <c r="E20" s="6">
         <v>17</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="15">
         <v>1138</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="17">
         <v>400</v>
       </c>
       <c r="I20" s="6">
@@ -1438,8 +1918,32 @@
       <c r="L20" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20" s="6">
+        <v>17</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1138</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>17</v>
+      </c>
+      <c r="R20" s="1">
+        <v>1138</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T20" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" s="6">
         <v>18</v>
       </c>
@@ -1455,13 +1959,13 @@
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="11">
         <v>1217</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="13">
         <v>500</v>
       </c>
       <c r="I21" s="6">
@@ -1476,8 +1980,32 @@
       <c r="L21" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21" s="6">
+        <v>18</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1217</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P21" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>18</v>
+      </c>
+      <c r="R21" s="1">
+        <v>1217</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T21" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" s="6">
         <v>19</v>
       </c>
@@ -1514,8 +2042,32 @@
       <c r="L22" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22" s="6">
+        <v>19</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1219</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>19</v>
+      </c>
+      <c r="R22" s="1">
+        <v>1219</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T22" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" s="6">
         <v>20</v>
       </c>
@@ -1552,8 +2104,32 @@
       <c r="L23" s="9">
         <v>300</v>
       </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="M23" s="6">
+        <v>20</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1220</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="9">
+        <v>300</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>20</v>
+      </c>
+      <c r="R23" s="1">
+        <v>1220</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T23" s="9">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" s="6">
         <v>21</v>
       </c>
@@ -1590,8 +2166,32 @@
       <c r="L24" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="M24" s="6">
+        <v>21</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1222</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P24" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>21</v>
+      </c>
+      <c r="R24" s="1">
+        <v>1222</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T24" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25" s="6">
         <v>22</v>
       </c>
@@ -1628,8 +2228,32 @@
       <c r="L25" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="M25" s="6">
+        <v>22</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1223</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>22</v>
+      </c>
+      <c r="R25" s="1">
+        <v>1223</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T25" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26" s="6">
         <v>23</v>
       </c>
@@ -1666,8 +2290,32 @@
       <c r="L26" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="M26" s="6">
+        <v>23</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1224</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P26" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>23</v>
+      </c>
+      <c r="R26" s="1">
+        <v>1224</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27" s="6">
         <v>24</v>
       </c>
@@ -1683,13 +2331,13 @@
       <c r="E27" s="6">
         <v>24</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="15">
         <v>1225</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="17">
         <v>500</v>
       </c>
       <c r="I27" s="6">
@@ -1704,8 +2352,32 @@
       <c r="L27" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="M27" s="6">
+        <v>24</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1225</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P27" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>24</v>
+      </c>
+      <c r="R27" s="1">
+        <v>1225</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T27" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" s="6">
         <v>25</v>
       </c>
@@ -1721,13 +2393,13 @@
       <c r="E28" s="6">
         <v>25</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="15">
         <v>1226</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="17">
         <v>500</v>
       </c>
       <c r="I28" s="6">
@@ -1742,8 +2414,32 @@
       <c r="L28" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="M28" s="6">
+        <v>25</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1226</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P28" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>25</v>
+      </c>
+      <c r="R28" s="1">
+        <v>1226</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T28" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" s="6">
         <v>26</v>
       </c>
@@ -1759,13 +2455,13 @@
       <c r="E29" s="6">
         <v>26</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="11">
         <v>1230</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="13">
         <v>500</v>
       </c>
       <c r="I29" s="6">
@@ -1780,8 +2476,32 @@
       <c r="L29" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="M29" s="6">
+        <v>26</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1230</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P29" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>26</v>
+      </c>
+      <c r="R29" s="1">
+        <v>1230</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T29" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30" s="6">
         <v>27</v>
       </c>
@@ -1818,8 +2538,32 @@
       <c r="L30" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="M30" s="6">
+        <v>27</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1236</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P30" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>27</v>
+      </c>
+      <c r="R30" s="1">
+        <v>1236</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="T30" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31" s="6">
         <v>28</v>
       </c>
@@ -1856,8 +2600,32 @@
       <c r="L31" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="M31" s="6">
+        <v>28</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1245</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P31" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>28</v>
+      </c>
+      <c r="R31" s="1">
+        <v>1245</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T31" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" s="6">
         <v>29</v>
       </c>
@@ -1894,8 +2662,32 @@
       <c r="L32" s="9">
         <v>450</v>
       </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="M32" s="6">
+        <v>29</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1247</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P32" s="9">
+        <v>450</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>29</v>
+      </c>
+      <c r="R32" s="1">
+        <v>1247</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T32" s="9">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33" s="6">
         <v>30</v>
       </c>
@@ -1932,8 +2724,32 @@
       <c r="L33" s="9">
         <v>450</v>
       </c>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" s="6">
+        <v>30</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1249</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P33" s="9">
+        <v>450</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>30</v>
+      </c>
+      <c r="R33" s="1">
+        <v>1249</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T33" s="9">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34" s="6">
         <v>31</v>
       </c>
@@ -1970,8 +2786,32 @@
       <c r="L34" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="M34" s="6">
+        <v>31</v>
+      </c>
+      <c r="N34" s="1">
+        <v>1261</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>31</v>
+      </c>
+      <c r="R34" s="1">
+        <v>1261</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T34" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35" s="6">
         <v>32</v>
       </c>
@@ -2008,8 +2848,32 @@
       <c r="L35" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="M35" s="6">
+        <v>32</v>
+      </c>
+      <c r="N35" s="1">
+        <v>1262</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>32</v>
+      </c>
+      <c r="R35" s="1">
+        <v>1262</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T35" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36" s="6">
         <v>33</v>
       </c>
@@ -2046,8 +2910,32 @@
       <c r="L36" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="M36" s="6">
+        <v>33</v>
+      </c>
+      <c r="N36" s="1">
+        <v>1263</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P36" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>33</v>
+      </c>
+      <c r="R36" s="1">
+        <v>1263</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T36" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37" s="6">
         <v>34</v>
       </c>
@@ -2084,8 +2972,32 @@
       <c r="L37" s="9">
         <v>500</v>
       </c>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="M37" s="6">
+        <v>34</v>
+      </c>
+      <c r="N37" s="1">
+        <v>1267</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P37" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>34</v>
+      </c>
+      <c r="R37" s="1">
+        <v>1267</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T37" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38" s="6">
         <v>35</v>
       </c>
@@ -2122,8 +3034,32 @@
       <c r="L38" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="M38" s="6">
+        <v>35</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1268</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P38" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>35</v>
+      </c>
+      <c r="R38" s="1">
+        <v>1268</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T38" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39" s="6">
         <v>36</v>
       </c>
@@ -2160,8 +3096,32 @@
       <c r="L39" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="M39" s="6">
+        <v>36</v>
+      </c>
+      <c r="N39" s="1">
+        <v>1269</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P39" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>36</v>
+      </c>
+      <c r="R39" s="1">
+        <v>1269</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T39" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40" s="6">
         <v>37</v>
       </c>
@@ -2198,8 +3158,32 @@
       <c r="L40" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="M40" s="6">
+        <v>37</v>
+      </c>
+      <c r="N40" s="1">
+        <v>1270</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P40" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>37</v>
+      </c>
+      <c r="R40" s="1">
+        <v>1270</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T40" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41" s="6">
         <v>38</v>
       </c>
@@ -2236,8 +3220,32 @@
       <c r="L41" s="10">
         <v>400</v>
       </c>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="M41" s="6">
+        <v>38</v>
+      </c>
+      <c r="N41" s="7">
+        <v>1271</v>
+      </c>
+      <c r="O41" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="P41" s="10">
+        <v>400</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>38</v>
+      </c>
+      <c r="R41" s="7">
+        <v>1271</v>
+      </c>
+      <c r="S41" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T41" s="10">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42" s="6">
         <v>39</v>
       </c>
@@ -2274,8 +3282,32 @@
       <c r="L42" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="M42" s="6">
+        <v>39</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1272</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P42" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>39</v>
+      </c>
+      <c r="R42" s="1">
+        <v>1272</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T42" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43" s="6">
         <v>40</v>
       </c>
@@ -2312,8 +3344,32 @@
       <c r="L43" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="M43" s="6">
+        <v>40</v>
+      </c>
+      <c r="N43" s="1">
+        <v>1273</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P43" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>40</v>
+      </c>
+      <c r="R43" s="1">
+        <v>1273</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T43" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44" s="6">
         <v>41</v>
       </c>
@@ -2350,8 +3406,32 @@
       <c r="L44" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="M44" s="6">
+        <v>41</v>
+      </c>
+      <c r="N44" s="1">
+        <v>1274</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P44" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>41</v>
+      </c>
+      <c r="R44" s="1">
+        <v>1274</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T44" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45" s="6">
         <v>42</v>
       </c>
@@ -2388,8 +3468,32 @@
       <c r="L45" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="M45" s="6">
+        <v>42</v>
+      </c>
+      <c r="N45" s="1">
+        <v>1276</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P45" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>42</v>
+      </c>
+      <c r="R45" s="1">
+        <v>1276</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T45" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
       <c r="A46" s="6">
         <v>43</v>
       </c>
@@ -2426,8 +3530,32 @@
       <c r="L46" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="M46" s="6">
+        <v>43</v>
+      </c>
+      <c r="N46" s="1">
+        <v>1277</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P46" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>43</v>
+      </c>
+      <c r="R46" s="1">
+        <v>1277</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T46" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
       <c r="A47" s="6">
         <v>44</v>
       </c>
@@ -2464,8 +3592,32 @@
       <c r="L47" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="M47" s="6">
+        <v>44</v>
+      </c>
+      <c r="N47" s="1">
+        <v>1278</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P47" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>44</v>
+      </c>
+      <c r="R47" s="1">
+        <v>1278</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T47" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
       <c r="A48" s="6">
         <v>45</v>
       </c>
@@ -2502,8 +3654,32 @@
       <c r="L48" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="M48" s="6">
+        <v>45</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1279</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P48" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>45</v>
+      </c>
+      <c r="R48" s="1">
+        <v>1279</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T48" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49" s="6">
         <v>46</v>
       </c>
@@ -2540,8 +3716,32 @@
       <c r="L49" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="M49" s="6">
+        <v>46</v>
+      </c>
+      <c r="N49" s="1">
+        <v>1280</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P49" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>46</v>
+      </c>
+      <c r="R49" s="1">
+        <v>1280</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T49" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50" s="6">
         <v>47</v>
       </c>
@@ -2578,8 +3778,32 @@
       <c r="L50" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="M50" s="6">
+        <v>47</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1281</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P50" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>47</v>
+      </c>
+      <c r="R50" s="1">
+        <v>1281</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T50" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
       <c r="A51" s="6">
         <v>48</v>
       </c>
@@ -2616,8 +3840,32 @@
       <c r="L51" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="M51" s="6">
+        <v>48</v>
+      </c>
+      <c r="N51" s="1">
+        <v>1282</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>48</v>
+      </c>
+      <c r="R51" s="1">
+        <v>1282</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T51" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
       <c r="A52" s="6">
         <v>49</v>
       </c>
@@ -2654,8 +3902,32 @@
       <c r="L52" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="M52" s="6">
+        <v>49</v>
+      </c>
+      <c r="N52" s="1">
+        <v>1283</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>49</v>
+      </c>
+      <c r="R52" s="1">
+        <v>1283</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T52" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
       <c r="A53" s="6">
         <v>50</v>
       </c>
@@ -2692,8 +3964,32 @@
       <c r="L53" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="M53" s="6">
+        <v>50</v>
+      </c>
+      <c r="N53" s="1">
+        <v>1284</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P53" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>50</v>
+      </c>
+      <c r="R53" s="1">
+        <v>1284</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T53" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
       <c r="A54" s="6">
         <v>51</v>
       </c>
@@ -2730,8 +4026,32 @@
       <c r="L54" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="M54" s="6">
+        <v>51</v>
+      </c>
+      <c r="N54" s="1">
+        <v>1285</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P54" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>51</v>
+      </c>
+      <c r="R54" s="1">
+        <v>1285</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T54" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
       <c r="A55" s="6">
         <v>52</v>
       </c>
@@ -2768,8 +4088,32 @@
       <c r="L55" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="M55" s="6">
+        <v>52</v>
+      </c>
+      <c r="N55" s="1">
+        <v>1287</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P55" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>52</v>
+      </c>
+      <c r="R55" s="1">
+        <v>1287</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T55" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
       <c r="A56" s="6">
         <v>53</v>
       </c>
@@ -2806,8 +4150,32 @@
       <c r="L56" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="M56" s="6">
+        <v>53</v>
+      </c>
+      <c r="N56" s="1">
+        <v>1288</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P56" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>53</v>
+      </c>
+      <c r="R56" s="1">
+        <v>1288</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T56" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
       <c r="A57" s="6">
         <v>54</v>
       </c>
@@ -2844,8 +4212,32 @@
       <c r="L57" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="M57" s="6">
+        <v>54</v>
+      </c>
+      <c r="N57" s="1">
+        <v>1289</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>54</v>
+      </c>
+      <c r="R57" s="1">
+        <v>1289</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T57" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58" s="6">
         <v>55</v>
       </c>
@@ -2882,8 +4274,32 @@
       <c r="L58" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="M58" s="6">
+        <v>55</v>
+      </c>
+      <c r="N58" s="1">
+        <v>1290</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P58" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>55</v>
+      </c>
+      <c r="R58" s="1">
+        <v>1290</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T58" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
       <c r="A59" s="6">
         <v>56</v>
       </c>
@@ -2920,8 +4336,32 @@
       <c r="L59" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="M59" s="6">
+        <v>56</v>
+      </c>
+      <c r="N59" s="1">
+        <v>1291</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>56</v>
+      </c>
+      <c r="R59" s="1">
+        <v>1291</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
       <c r="A60" s="6">
         <v>57</v>
       </c>
@@ -2958,8 +4398,32 @@
       <c r="L60" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="M60" s="6">
+        <v>57</v>
+      </c>
+      <c r="N60" s="1">
+        <v>1292</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P60" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>57</v>
+      </c>
+      <c r="R60" s="1">
+        <v>1292</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T60" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
       <c r="A61" s="6">
         <v>58</v>
       </c>
@@ -2996,8 +4460,32 @@
       <c r="L61" s="9">
         <v>210</v>
       </c>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="M61" s="6">
+        <v>58</v>
+      </c>
+      <c r="N61" s="1">
+        <v>1293</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P61" s="9">
+        <v>210</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>58</v>
+      </c>
+      <c r="R61" s="1">
+        <v>1293</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T61" s="9">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
       <c r="A62" s="6">
         <v>59</v>
       </c>
@@ -3034,8 +4522,32 @@
       <c r="L62" s="9">
         <v>400</v>
       </c>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="M62" s="6">
+        <v>59</v>
+      </c>
+      <c r="N62" s="1">
+        <v>1298</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P62" s="9">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>59</v>
+      </c>
+      <c r="R62" s="1">
+        <v>1298</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T62" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
       <c r="A63" s="6">
         <v>60</v>
       </c>
@@ -3072,12 +4584,46 @@
       <c r="L63" s="9">
         <v>500</v>
       </c>
+      <c r="M63" s="6">
+        <v>60</v>
+      </c>
+      <c r="N63" s="1">
+        <v>1299</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P63" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>60</v>
+      </c>
+      <c r="R63" s="1">
+        <v>1299</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T63" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="66" spans="7:7">
+      <c r="G66" s="14"/>
+    </row>
+    <row r="67" spans="7:7">
+      <c r="G67" s="18"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:D63">
     <sortCondition ref="B4:B63"/>
   </sortState>
-  <mergeCells count="6">
+  <mergeCells count="10">
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="M2:P2"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E1:H1"/>
